--- a/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>LEGN</t>
   </si>
@@ -774,22 +774,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>822800</v>
+        <v>408100</v>
       </c>
       <c r="E9" s="3">
-        <v>648100</v>
+        <v>234600</v>
       </c>
       <c r="F9" s="3">
-        <v>526400</v>
+        <v>144200</v>
       </c>
       <c r="G9" s="3">
-        <v>401000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>313300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>232200</v>
+        <v>65400</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -819,22 +819,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>206100</v>
+        <v>620800</v>
       </c>
       <c r="E10" s="3">
-        <v>-20800</v>
+        <v>392700</v>
       </c>
       <c r="F10" s="3">
-        <v>-241300</v>
+        <v>140900</v>
       </c>
       <c r="G10" s="3">
-        <v>-284000</v>
+        <v>51600</v>
       </c>
       <c r="H10" s="3">
-        <v>-244500</v>
+        <v>68800</v>
       </c>
       <c r="I10" s="3">
-        <v>-157200</v>
+        <v>75000</v>
       </c>
       <c r="J10" s="3">
         <v>61800</v>
